--- a/sources/gunjack_step3.xlsx
+++ b/sources/gunjack_step3.xlsx
@@ -1083,6 +1083,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>ebd747c4-4a3a-4cb9-96c6-6ce86ed0ce58</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>ebd747c4-4a3a-4cb9-96c6-6ce86ed0ce58</t>
@@ -1120,6 +1125,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>e5ab66b0-1617-4024-933b-69248c5a2646</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>e5ab66b0-1617-4024-933b-69248c5a2646</t>
@@ -1162,6 +1172,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>48ad3fb6-8248-4bd4-b552-f8a579f06b84</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>48ad3fb6-8248-4bd4-b552-f8a579f06b84</t>
@@ -1199,6 +1214,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>dc329630-4a74-4808-906f-cc4361fed63a</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>dc329630-4a74-4808-906f-cc4361fed63a</t>
@@ -1236,6 +1256,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>b792ea67-ccd8-406a-8717-ceff6184d4ad</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>b792ea67-ccd8-406a-8717-ceff6184d4ad</t>
@@ -1271,6 +1296,11 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>251f1e2f-c3c7-4333-a3d4-49d19c52d36c</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -5961,6 +5991,11 @@
           <t>sLLmmmmmmm</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
+        </is>
+      </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
@@ -5988,6 +6023,11 @@
           <t>sLLmmmmmlm</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
+        </is>
+      </c>
       <c r="O117" t="inlineStr">
         <is>
           <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
@@ -6015,6 +6055,11 @@
           <t>hmLLLmmmmm</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
+        </is>
+      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
@@ -6040,6 +6085,11 @@
       <c r="I119" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>2fc42861-9255-4a82-8966-00993ca4d00e</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
